--- a/Data/Home/BedroomTwo.Door001.xlsx
+++ b/Data/Home/BedroomTwo.Door001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H503"/>
+  <dimension ref="A1:I509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709249165</v>
+        <v>1711841298</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709250382</v>
+        <v>1711842323</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709251467</v>
+        <v>1711844095</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709252289</v>
+        <v>1711845293</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709262176</v>
+        <v>1711874004</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709262186</v>
+        <v>1711874029</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709262450</v>
+        <v>1711874158</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709262578</v>
+        <v>1711874167</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709265242</v>
+        <v>1711877381</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709265279</v>
+        <v>1711877396</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709266248</v>
+        <v>1711877873</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709266275</v>
+        <v>1711877881</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709280523</v>
+        <v>1711879347</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709280541</v>
+        <v>1711879361</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709281040</v>
+        <v>1711888075</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709281582</v>
+        <v>1711888092</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709282441</v>
+        <v>1711926538</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709282459</v>
+        <v>1711927582</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709282684</v>
+        <v>1711928958</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709283954</v>
+        <v>1711930039</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709285781</v>
+        <v>1711959620</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709285793</v>
+        <v>1711959632</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709286442</v>
+        <v>1711962363</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709287682</v>
+        <v>1711962375</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709289639</v>
+        <v>1711964500</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709244509</v>
+        <v>1711964513</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709245217</v>
+        <v>1711965112</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709246079</v>
+        <v>1711965131</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709266695</v>
+        <v>1711968996</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709266711</v>
+        <v>1711969004</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709267046</v>
+        <v>1711980849</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709267059</v>
+        <v>1711980868</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709267125</v>
+        <v>1712014021</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709268370</v>
+        <v>1712015070</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709268856</v>
+        <v>1712018097</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709268869</v>
+        <v>1712019103</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709270205</v>
+        <v>1712051410</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709270222</v>
+        <v>1712051433</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709270807</v>
+        <v>1712055546</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709272666</v>
+        <v>1712055553</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709274429</v>
+        <v>1712055658</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709330175</v>
+        <v>1712055662</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709330985</v>
+        <v>1712058365</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709331897</v>
+        <v>1712058375</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709349498</v>
+        <v>1712060345</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709349521</v>
+        <v>1712060362</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709349956</v>
+        <v>1712064478</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709351473</v>
+        <v>1712064500</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709357214</v>
+        <v>1712100412</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709357228</v>
+        <v>1712101500</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709359037</v>
+        <v>1712102712</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2360,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709359071</v>
+        <v>1712103745</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709360115</v>
+        <v>1712138280</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709361353</v>
+        <v>1712138298</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709363037</v>
+        <v>1712139100</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709363048</v>
+        <v>1712139112</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709363636</v>
+        <v>1712141614</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709417097</v>
+        <v>1712141626</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709417668</v>
+        <v>1712141643</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709418510</v>
+        <v>1712141653</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709448723</v>
+        <v>1712143531</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709448749</v>
+        <v>1712143541</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709449216</v>
+        <v>1712157256</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709451144</v>
+        <v>1712157280</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709451738</v>
+        <v>1712186790</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709451755</v>
+        <v>1712187820</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709453119</v>
+        <v>1712189051</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709454169</v>
+        <v>1712190110</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709455964</v>
+        <v>1712216188</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3026,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709455979</v>
+        <v>1712216210</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709456665</v>
+        <v>1712217614</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709456818</v>
+        <v>1712217619</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709458903</v>
+        <v>1712220054</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709502418</v>
+        <v>1712220061</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709503333</v>
+        <v>1712220605</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709504141</v>
+        <v>1712220613</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709515569</v>
+        <v>1712222662</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709515582</v>
+        <v>1712222672</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3359,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709519767</v>
+        <v>1712233725</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3396,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709519782</v>
+        <v>1712233748</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709526995</v>
+        <v>1712273228</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3470,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709527012</v>
+        <v>1712274254</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3507,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709528315</v>
+        <v>1712276986</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3544,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709529685</v>
+        <v>1712278111</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3581,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709531453</v>
+        <v>1712289352</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709531465</v>
+        <v>1712289361</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3655,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709532061</v>
+        <v>1712294360</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3692,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709533791</v>
+        <v>1712294371</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709534408</v>
+        <v>1712306209</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3766,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709536783</v>
+        <v>1712306229</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3803,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709549438</v>
+        <v>1712310224</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3840,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709549455</v>
+        <v>1712310228</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709551338</v>
+        <v>1712316634</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +3914,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709588940</v>
+        <v>1712316648</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +3951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709590075</v>
+        <v>1712320724</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +3988,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709590974</v>
+        <v>1712320736</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4025,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709612701</v>
+        <v>1712323362</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709612738</v>
+        <v>1712323370</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709613283</v>
+        <v>1712325414</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709615662</v>
+        <v>1712325420</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4173,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709622354</v>
+        <v>1712363692</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709622365</v>
+        <v>1712368628</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4247,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709624021</v>
+        <v>1712370912</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4284,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709631107</v>
+        <v>1712371540</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4321,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709632557</v>
+        <v>1712401945</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4358,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709633518</v>
+        <v>1712402018</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4395,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709635074</v>
+        <v>1712406440</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709635089</v>
+        <v>1712406473</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709635636</v>
+        <v>1712407960</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709683453</v>
+        <v>1712407969</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709685198</v>
+        <v>1712408648</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4580,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709685709</v>
+        <v>1712408654</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709711005</v>
+        <v>1712411810</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4654,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709711053</v>
+        <v>1712411816</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709711897</v>
+        <v>1712420554</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4728,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709712394</v>
+        <v>1712420601</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709713372</v>
+        <v>1712450011</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4802,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1709715919</v>
+        <v>1712455591</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4839,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4858,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1709716410</v>
+        <v>1712456635</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +4876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4895,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1709716426</v>
+        <v>1712457396</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4913,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4932,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1709716460</v>
+        <v>1712485648</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +4950,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4969,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1709716478</v>
+        <v>1712485701</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +4987,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5006,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1709716946</v>
+        <v>1712489059</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5024,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5043,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1709722710</v>
+        <v>1712489092</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4933,6 +5061,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5080,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1709763811</v>
+        <v>1712491245</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5098,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5117,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1709769415</v>
+        <v>1712491254</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,6 +5135,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5023,7 +5154,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1709770681</v>
+        <v>1712495855</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5041,6 +5172,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5059,7 +5191,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1709771276</v>
+        <v>1712495862</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5077,6 +5209,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5228,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1709795864</v>
+        <v>1712496436</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5113,6 +5246,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5131,7 +5265,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1709795895</v>
+        <v>1712496449</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5149,6 +5283,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5167,7 +5302,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1709796699</v>
+        <v>1712497980</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5185,6 +5320,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5203,7 +5339,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1709798372</v>
+        <v>1712498033</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5221,6 +5357,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5376,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1709798992</v>
+        <v>1712532033</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5257,6 +5394,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5413,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1709799005</v>
+        <v>1712533241</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5293,6 +5431,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5450,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1709799264</v>
+        <v>1712534542</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5329,6 +5468,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5347,7 +5487,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1709804222</v>
+        <v>1712535544</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5365,6 +5505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5383,7 +5524,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1709804755</v>
+        <v>1712552738</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5401,6 +5542,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5561,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1709804771</v>
+        <v>1712552746</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5437,6 +5579,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5598,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1709848091</v>
+        <v>1712556702</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5473,6 +5616,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5491,7 +5635,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1709848911</v>
+        <v>1712556709</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5509,6 +5653,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5527,7 +5672,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1709851554</v>
+        <v>1712568544</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5545,6 +5690,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5563,7 +5709,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1709852284</v>
+        <v>1712568555</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5581,6 +5727,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5746,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1709860391</v>
+        <v>1712569285</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5617,6 +5764,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5635,7 +5783,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1709860408</v>
+        <v>1712569312</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5801,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +5820,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1709860666</v>
+        <v>1712571421</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5689,6 +5838,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5707,7 +5857,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1709863297</v>
+        <v>1712571428</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5725,6 +5875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5743,7 +5894,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1709872560</v>
+        <v>1712572410</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5761,6 +5912,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +5931,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1709872576</v>
+        <v>1712572420</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5797,6 +5949,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5815,7 +5968,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1709873127</v>
+        <v>1712573432</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5833,6 +5986,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5851,7 +6005,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1709874738</v>
+        <v>1712573445</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5869,6 +6023,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6042,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1709879892</v>
+        <v>1712579366</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5905,6 +6060,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5923,7 +6079,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1709879907</v>
+        <v>1712579388</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5941,6 +6097,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5959,7 +6116,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1709880637</v>
+        <v>1712618592</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5977,6 +6134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6153,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1709880645</v>
+        <v>1712619649</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6190,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1709881716</v>
+        <v>1712622973</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6208,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6227,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1709883016</v>
+        <v>1712624017</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6264,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1709883672</v>
+        <v>1712646186</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6121,6 +6282,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6139,7 +6301,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1709884834</v>
+        <v>1712646218</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6157,6 +6319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6338,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1709885503</v>
+        <v>1712650706</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6356,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6375,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1709936047</v>
+        <v>1712650711</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6229,6 +6393,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6247,7 +6412,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1709937367</v>
+        <v>1712654325</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6265,6 +6430,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6283,7 +6449,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1709938189</v>
+        <v>1712654336</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6301,6 +6467,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6319,7 +6486,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1709962492</v>
+        <v>1712656956</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6337,6 +6504,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6355,7 +6523,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1709962506</v>
+        <v>1712656969</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6373,6 +6541,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6391,7 +6560,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1709963814</v>
+        <v>1712658970</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6409,6 +6578,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6427,7 +6597,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1709964669</v>
+        <v>1712658981</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6445,6 +6615,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6463,7 +6634,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1709966400</v>
+        <v>1712662222</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6481,6 +6652,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6499,7 +6671,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1709966408</v>
+        <v>1712662242</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6517,6 +6689,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6535,7 +6708,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1709966846</v>
+        <v>1712704975</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6553,6 +6726,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6571,7 +6745,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1709966865</v>
+        <v>1712706003</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6589,6 +6763,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6607,7 +6782,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1709966911</v>
+        <v>1712707063</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6625,6 +6800,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6643,7 +6819,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1709969871</v>
+        <v>1712708171</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6661,6 +6837,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6679,7 +6856,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1709978385</v>
+        <v>1712720251</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6697,6 +6874,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6715,7 +6893,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1709978404</v>
+        <v>1712720261</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6733,6 +6911,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6751,7 +6930,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1709980513</v>
+        <v>1712724414</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6769,6 +6948,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6787,7 +6967,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710022263</v>
+        <v>1712724431</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6805,6 +6985,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6823,7 +7004,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710023100</v>
+        <v>1712737177</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6841,6 +7022,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6859,7 +7041,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710023949</v>
+        <v>1712737206</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6877,6 +7059,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6895,7 +7078,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710034884</v>
+        <v>1712741487</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6913,6 +7096,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6931,7 +7115,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710034898</v>
+        <v>1712741499</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6949,6 +7133,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6967,7 +7152,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710038607</v>
+        <v>1712741554</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6985,6 +7170,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7003,7 +7189,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710038640</v>
+        <v>1712741559</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7021,6 +7207,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7039,7 +7226,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710050852</v>
+        <v>1712744230</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7057,6 +7244,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7075,7 +7263,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710050868</v>
+        <v>1712744240</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7093,6 +7281,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7111,7 +7300,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710052315</v>
+        <v>1712746225</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7129,6 +7318,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7147,7 +7337,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710053540</v>
+        <v>1712746234</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7165,6 +7355,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7183,7 +7374,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710055159</v>
+        <v>1712747720</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7201,6 +7392,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7219,7 +7411,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710055167</v>
+        <v>1712747737</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7237,6 +7429,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7255,7 +7448,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710055374</v>
+        <v>1712790384</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7273,6 +7466,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7291,7 +7485,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710055396</v>
+        <v>1712791445</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7309,6 +7503,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7327,7 +7522,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710055694</v>
+        <v>1712792899</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7345,6 +7540,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7363,7 +7559,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710058114</v>
+        <v>1712793901</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7381,6 +7577,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7399,7 +7596,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710063819</v>
+        <v>1712805441</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7417,6 +7614,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7435,7 +7633,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710063831</v>
+        <v>1712805450</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7453,6 +7651,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7471,7 +7670,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710065877</v>
+        <v>1712809533</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7489,6 +7688,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7507,7 +7707,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710107825</v>
+        <v>1712809562</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7525,6 +7725,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7543,7 +7744,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710108430</v>
+        <v>1712820454</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7561,6 +7762,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7579,7 +7781,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710109209</v>
+        <v>1712820478</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7597,6 +7799,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7615,7 +7818,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710134964</v>
+        <v>1712824041</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7633,6 +7836,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7651,7 +7855,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710134985</v>
+        <v>1712824054</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7669,6 +7873,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7687,7 +7892,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710135573</v>
+        <v>1712827777</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7705,6 +7910,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7723,7 +7929,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710138064</v>
+        <v>1712827789</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -7741,6 +7947,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7759,7 +7966,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710147708</v>
+        <v>1712830451</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7777,6 +7984,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7795,7 +8003,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710147719</v>
+        <v>1712830460</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7813,6 +8021,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7831,7 +8040,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710148108</v>
+        <v>1712832332</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7849,6 +8058,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7867,7 +8077,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710148117</v>
+        <v>1712832339</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7885,6 +8095,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7903,7 +8114,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710149402</v>
+        <v>1712835515</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7921,6 +8132,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7939,7 +8151,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710150462</v>
+        <v>1712835530</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7957,6 +8169,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7975,7 +8188,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710151767</v>
+        <v>1712877062</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7993,6 +8206,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8011,7 +8225,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710152281</v>
+        <v>1712878070</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8029,6 +8243,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8047,7 +8262,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710152291</v>
+        <v>1712879015</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -8065,6 +8280,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8083,7 +8299,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710196023</v>
+        <v>1712880136</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -8101,6 +8317,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8119,7 +8336,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710197616</v>
+        <v>1712895085</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -8137,6 +8354,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8155,7 +8373,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710198553</v>
+        <v>1712895095</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -8173,6 +8391,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8191,7 +8410,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710220128</v>
+        <v>1712900412</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -8209,6 +8428,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8227,7 +8447,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710220154</v>
+        <v>1712900421</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -8245,6 +8465,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8263,7 +8484,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710220672</v>
+        <v>1712912979</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -8281,6 +8502,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8299,7 +8521,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710223054</v>
+        <v>1712913001</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -8317,6 +8539,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8335,7 +8558,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710223158</v>
+        <v>1712915316</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -8353,6 +8576,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8371,7 +8595,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710223173</v>
+        <v>1712915328</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -8389,6 +8613,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8407,7 +8632,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710224314</v>
+        <v>1712916604</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -8425,6 +8650,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8443,7 +8669,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710225572</v>
+        <v>1712916611</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8461,6 +8687,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8479,7 +8706,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710227433</v>
+        <v>1712918429</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8497,6 +8724,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8515,7 +8743,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710227448</v>
+        <v>1712918439</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8533,6 +8761,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8551,7 +8780,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710228054</v>
+        <v>1712920508</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8569,6 +8798,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8587,7 +8817,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710238964</v>
+        <v>1712920517</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -8605,6 +8835,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8623,7 +8854,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710241124</v>
+        <v>1712926484</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8641,6 +8872,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8659,7 +8891,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710291164</v>
+        <v>1712926508</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8677,6 +8909,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8695,7 +8928,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710296728</v>
+        <v>1712968754</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -8713,6 +8946,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8731,7 +8965,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710297238</v>
+        <v>1712973225</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -8749,6 +8983,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8767,7 +9002,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710319279</v>
+        <v>1712980617</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -8785,6 +9020,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8803,7 +9039,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710319324</v>
+        <v>1712981446</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -8821,6 +9057,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8839,7 +9076,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710320234</v>
+        <v>1713007599</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -8857,6 +9094,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8875,7 +9113,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710324266</v>
+        <v>1713007663</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -8893,6 +9131,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8911,7 +9150,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1710324778</v>
+        <v>1713009562</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8929,6 +9168,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8947,7 +9187,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1710324795</v>
+        <v>1713009641</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8965,6 +9205,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8983,7 +9224,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1710325642</v>
+        <v>1713014066</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -9001,6 +9242,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9019,7 +9261,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1710325658</v>
+        <v>1713014075</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -9037,6 +9279,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9055,7 +9298,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1710326564</v>
+        <v>1713014685</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -9073,6 +9316,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9091,7 +9335,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1710329617</v>
+        <v>1713014693</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -9109,6 +9353,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9127,7 +9372,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1710330093</v>
+        <v>1713015373</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -9145,6 +9390,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9163,7 +9409,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1710334990</v>
+        <v>1713015382</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -9181,6 +9427,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9199,7 +9446,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1710370112</v>
+        <v>1713023892</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -9217,6 +9464,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9235,7 +9483,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1710375477</v>
+        <v>1713023968</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -9253,6 +9501,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9271,7 +9520,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1710377406</v>
+        <v>1713054231</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -9289,6 +9538,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9307,7 +9557,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1710378106</v>
+        <v>1713060213</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -9325,6 +9575,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9343,7 +9594,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1710404193</v>
+        <v>1713063957</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -9361,6 +9612,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9379,7 +9631,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1710404221</v>
+        <v>1713064628</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -9397,6 +9649,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9415,7 +9668,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1710404439</v>
+        <v>1713095000</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -9433,6 +9686,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9451,7 +9705,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1710404501</v>
+        <v>1713095070</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -9469,6 +9723,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9487,7 +9742,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1710405044</v>
+        <v>1713101653</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -9505,6 +9760,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9523,7 +9779,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1710407648</v>
+        <v>1713101708</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -9541,6 +9797,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9559,7 +9816,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1710408120</v>
+        <v>1713102432</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -9577,6 +9834,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9595,7 +9853,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1710408893</v>
+        <v>1713102446</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -9613,6 +9871,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9631,7 +9890,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1710409437</v>
+        <v>1713103149</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -9649,6 +9908,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9667,7 +9927,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1710409445</v>
+        <v>1713103157</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -9685,6 +9945,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9703,7 +9964,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1710454898</v>
+        <v>1713107830</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -9721,6 +9982,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9739,7 +10001,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1710455791</v>
+        <v>1713107841</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -9757,6 +10019,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9775,7 +10038,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1710456725</v>
+        <v>1713115573</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -9793,6 +10056,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9811,7 +10075,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1710457757</v>
+        <v>1713115672</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -9829,6 +10093,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9847,7 +10112,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1710484752</v>
+        <v>1713137012</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -9865,6 +10130,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9883,7 +10149,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1710484760</v>
+        <v>1713137997</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -9901,6 +10167,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9919,7 +10186,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1710485969</v>
+        <v>1713139026</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -9937,6 +10204,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9955,7 +10223,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1710486850</v>
+        <v>1713140140</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -9973,6 +10241,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9991,7 +10260,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1710488409</v>
+        <v>1713177407</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -10009,6 +10278,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10027,7 +10297,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1710488425</v>
+        <v>1713177435</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -10045,6 +10315,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10063,7 +10334,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1710488916</v>
+        <v>1713181444</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -10081,6 +10352,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10099,7 +10371,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1710489104</v>
+        <v>1713181454</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -10117,6 +10389,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10135,7 +10408,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1710489612</v>
+        <v>1713182306</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -10153,6 +10426,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10171,7 +10445,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1710491578</v>
+        <v>1713182316</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -10189,6 +10463,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10207,7 +10482,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1710498628</v>
+        <v>1713185491</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -10225,6 +10500,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10243,7 +10519,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1710498651</v>
+        <v>1713185500</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -10261,6 +10537,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10279,7 +10556,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1710500651</v>
+        <v>1713187596</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -10297,6 +10574,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10315,7 +10593,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1710540885</v>
+        <v>1713187610</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -10333,6 +10611,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10351,7 +10630,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1710541260</v>
+        <v>1713190819</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -10369,6 +10648,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10387,7 +10667,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1710542069</v>
+        <v>1713190835</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -10405,6 +10685,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10423,7 +10704,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1710551771</v>
+        <v>1713223099</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -10441,6 +10722,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10459,7 +10741,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1710551787</v>
+        <v>1713224184</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -10477,6 +10759,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10495,7 +10778,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1710555005</v>
+        <v>1713225454</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -10513,6 +10796,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10531,7 +10815,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1710555039</v>
+        <v>1713226508</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -10549,6 +10833,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10567,7 +10852,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1710563944</v>
+        <v>1713242511</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -10585,6 +10870,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10603,7 +10889,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1710563967</v>
+        <v>1713242519</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -10621,6 +10907,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10639,7 +10926,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1710564427</v>
+        <v>1713247526</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -10657,6 +10944,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10675,7 +10963,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1710566222</v>
+        <v>1713247535</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -10693,6 +10981,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10711,7 +11000,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1710573849</v>
+        <v>1713260504</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -10729,6 +11018,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10747,7 +11037,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1710573858</v>
+        <v>1713260515</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -10765,6 +11055,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10783,7 +11074,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1710574768</v>
+        <v>1713263806</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -10801,6 +11092,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10819,7 +11111,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1710574785</v>
+        <v>1713263816</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -10837,6 +11129,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10855,7 +11148,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1710575326</v>
+        <v>1713265942</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -10873,6 +11166,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10891,7 +11185,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1710576297</v>
+        <v>1713265947</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -10909,6 +11203,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10927,7 +11222,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1710576661</v>
+        <v>1713267331</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -10945,6 +11240,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10963,7 +11259,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1710578062</v>
+        <v>1713267353</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -10981,6 +11277,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10999,7 +11296,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1710578552</v>
+        <v>1713271213</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -11017,6 +11314,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11035,7 +11333,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1710626820</v>
+        <v>1713271221</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -11053,6 +11351,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11071,7 +11370,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1710627682</v>
+        <v>1713283679</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -11089,6 +11388,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11107,7 +11407,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1710628533</v>
+        <v>1713283697</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -11125,6 +11425,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11143,7 +11444,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1710658049</v>
+        <v>1713309876</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -11161,6 +11462,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11179,7 +11481,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1710658071</v>
+        <v>1713310812</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -11197,6 +11499,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11215,7 +11518,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1710659287</v>
+        <v>1713313389</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -11233,6 +11536,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11251,7 +11555,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1710659393</v>
+        <v>1713314519</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -11269,6 +11573,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11287,7 +11592,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1710659844</v>
+        <v>1713326365</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -11305,6 +11610,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11323,7 +11629,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1710660576</v>
+        <v>1713326375</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -11341,6 +11647,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11359,7 +11666,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1710662021</v>
+        <v>1713327791</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -11377,6 +11684,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11395,7 +11703,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1710662043</v>
+        <v>1713327807</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -11413,6 +11721,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11431,7 +11740,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1710662338</v>
+        <v>1713330398</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -11449,6 +11758,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11467,7 +11777,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1710662357</v>
+        <v>1713330417</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -11485,6 +11795,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11503,7 +11814,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1710662868</v>
+        <v>1713332482</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -11521,6 +11832,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11539,7 +11851,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1710670670</v>
+        <v>1713332493</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -11557,6 +11869,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11575,7 +11888,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1710672719</v>
+        <v>1713343182</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -11593,6 +11906,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11611,7 +11925,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1710713351</v>
+        <v>1713343210</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -11629,6 +11943,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11647,7 +11962,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1710714580</v>
+        <v>1713346664</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -11665,6 +11980,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11683,7 +11999,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1710715568</v>
+        <v>1713346681</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -11701,6 +12017,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11719,7 +12036,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1710737472</v>
+        <v>1713351491</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -11737,6 +12054,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11755,7 +12073,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1710737492</v>
+        <v>1713351500</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -11773,6 +12091,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11791,7 +12110,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1710738645</v>
+        <v>1713354287</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -11809,6 +12128,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11827,7 +12147,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1710739324</v>
+        <v>1713354294</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -11845,6 +12165,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11863,7 +12184,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1710739684</v>
+        <v>1713355726</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -11881,6 +12202,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11899,7 +12221,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1710739697</v>
+        <v>1713355741</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -11917,6 +12239,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11935,7 +12258,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1710739793</v>
+        <v>1713356189</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -11953,6 +12276,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11971,7 +12295,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1710741387</v>
+        <v>1713356202</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -11989,6 +12313,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12007,7 +12332,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1710741864</v>
+        <v>1713395504</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -12025,6 +12350,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12043,7 +12369,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1710742516</v>
+        <v>1713396667</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -12061,6 +12387,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12079,7 +12406,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1710747953</v>
+        <v>1713397860</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -12097,6 +12424,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12115,7 +12443,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1710747976</v>
+        <v>1713398974</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -12133,6 +12461,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12151,7 +12480,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1710749779</v>
+        <v>1713412330</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -12169,6 +12498,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12187,7 +12517,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1710799477</v>
+        <v>1713412341</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -12205,6 +12535,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12223,7 +12554,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1710800247</v>
+        <v>1713417232</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -12241,6 +12572,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12259,7 +12591,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1710801220</v>
+        <v>1713417242</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -12277,6 +12609,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12295,7 +12628,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1710827890</v>
+        <v>1713437416</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -12313,6 +12646,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12331,7 +12665,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1710827902</v>
+        <v>1713437430</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -12349,6 +12683,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12367,7 +12702,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1710829269</v>
+        <v>1713440212</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -12385,6 +12720,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12403,7 +12739,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1710830315</v>
+        <v>1713440235</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -12421,6 +12757,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12439,7 +12776,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1710831927</v>
+        <v>1713440303</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -12457,6 +12794,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12475,7 +12813,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1710831937</v>
+        <v>1713440310</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -12493,6 +12831,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12511,7 +12850,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1710832431</v>
+        <v>1713442194</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -12529,6 +12868,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12547,7 +12887,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1710833953</v>
+        <v>1713442211</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -12565,6 +12905,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12583,7 +12924,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1710834376</v>
+        <v>1713443753</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -12601,6 +12942,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12619,7 +12961,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1710835710</v>
+        <v>1713443760</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -12637,6 +12979,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12655,7 +12998,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1710841588</v>
+        <v>1713451189</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -12673,6 +13016,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12691,7 +13035,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1710841601</v>
+        <v>1713451206</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -12709,6 +13053,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12727,7 +13072,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1710843317</v>
+        <v>1713482164</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -12745,6 +13090,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12763,7 +13109,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1710890867</v>
+        <v>1713483279</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -12781,6 +13127,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12799,7 +13146,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1710895595</v>
+        <v>1713486685</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -12817,6 +13164,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12835,7 +13183,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1710896177</v>
+        <v>1713487662</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -12853,6 +13201,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12871,7 +13220,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1710917533</v>
+        <v>1713518350</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -12889,6 +13238,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12907,7 +13257,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1710917569</v>
+        <v>1713518365</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -12925,6 +13275,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12943,7 +13294,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1710918551</v>
+        <v>1713520965</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -12961,6 +13312,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12979,7 +13331,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1710922280</v>
+        <v>1713520982</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -12997,6 +13349,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13015,7 +13368,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1710922877</v>
+        <v>1713522704</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -13033,6 +13386,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -13051,7 +13405,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1710922895</v>
+        <v>1713522718</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -13069,6 +13423,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13087,7 +13442,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1710924315</v>
+        <v>1713526199</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -13105,6 +13460,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13123,7 +13479,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1710924341</v>
+        <v>1713526225</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -13141,6 +13497,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -13159,7 +13516,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1710925200</v>
+        <v>1713529928</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -13177,6 +13534,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -13195,7 +13553,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1710928402</v>
+        <v>1713529936</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -13213,6 +13571,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -13231,7 +13590,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1710928885</v>
+        <v>1713536491</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -13249,6 +13608,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -13267,7 +13627,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1710934203</v>
+        <v>1713536514</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -13285,6 +13645,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -13303,7 +13664,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1710973910</v>
+        <v>1713573577</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -13321,6 +13682,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13339,7 +13701,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1710979239</v>
+        <v>1713578339</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -13357,6 +13719,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13375,7 +13738,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1710982681</v>
+        <v>1713580326</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -13393,6 +13756,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -13411,7 +13775,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1710983308</v>
+        <v>1713580954</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -13429,6 +13793,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -13447,7 +13812,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1711005783</v>
+        <v>1713616839</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -13465,6 +13830,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -13483,7 +13849,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1711005817</v>
+        <v>1713616882</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -13501,6 +13867,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -13519,7 +13886,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1711006687</v>
+        <v>1713619447</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -13537,6 +13904,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13555,7 +13923,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1711010082</v>
+        <v>1713619519</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -13573,6 +13941,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13591,7 +13960,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1711010929</v>
+        <v>1713623569</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -13609,6 +13978,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13627,7 +13997,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1711010952</v>
+        <v>1713623579</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -13645,6 +14015,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13663,7 +14034,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1711011094</v>
+        <v>1713624222</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -13681,6 +14052,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13699,7 +14071,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1711011450</v>
+        <v>1713624231</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -13717,6 +14089,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13735,7 +14108,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1711013919</v>
+        <v>1713625602</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -13753,6 +14126,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13771,7 +14145,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1711013940</v>
+        <v>1713625615</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -13789,6 +14163,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13807,7 +14182,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1711014338</v>
+        <v>1713632363</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -13825,6 +14200,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13843,7 +14219,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1711019837</v>
+        <v>1713632426</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -13861,6 +14237,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13879,7 +14256,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1711058299</v>
+        <v>1713658395</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -13897,6 +14274,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13915,7 +14293,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1711059226</v>
+        <v>1713664413</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -13933,6 +14311,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13951,7 +14330,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1711060465</v>
+        <v>1713665772</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -13969,6 +14348,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13987,7 +14367,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1711061404</v>
+        <v>1713666330</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -14005,6 +14385,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14023,7 +14404,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1711071421</v>
+        <v>1713696566</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -14041,6 +14422,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -14059,7 +14441,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1711071426</v>
+        <v>1713696622</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -14077,6 +14459,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14095,7 +14478,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1711071565</v>
+        <v>1713701314</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -14113,6 +14496,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14131,7 +14515,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1711071578</v>
+        <v>1713701384</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -14149,6 +14533,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -14167,7 +14552,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1711071727</v>
+        <v>1713702604</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -14185,6 +14570,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14203,7 +14589,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1711074311</v>
+        <v>1713702620</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -14221,6 +14607,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -14239,7 +14626,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1711075091</v>
+        <v>1713703311</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -14257,6 +14644,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -14275,7 +14663,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1711075119</v>
+        <v>1713703317</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -14293,6 +14681,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -14311,7 +14700,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1711086679</v>
+        <v>1713706463</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -14329,6 +14718,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -14347,7 +14737,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1711086706</v>
+        <v>1713706471</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -14365,6 +14755,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14383,7 +14774,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1711087260</v>
+        <v>1713713831</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -14401,6 +14792,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14419,7 +14811,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1711088670</v>
+        <v>1713713900</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -14437,6 +14829,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14455,7 +14848,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1711089192</v>
+        <v>1713740271</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -14473,6 +14866,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14491,7 +14885,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1711089201</v>
+        <v>1713741266</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -14509,6 +14903,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -14527,7 +14922,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1711090316</v>
+        <v>1713742822</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -14545,6 +14940,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -14563,7 +14959,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1711091034</v>
+        <v>1713743908</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -14581,6 +14977,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -14599,7 +14996,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1711092496</v>
+        <v>1713772148</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -14617,6 +15014,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -14635,7 +15033,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1711092513</v>
+        <v>1713772170</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -14653,6 +15051,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -14671,7 +15070,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1711092872</v>
+        <v>1713774847</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -14689,6 +15088,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -14707,7 +15107,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1711095477</v>
+        <v>1713774855</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -14725,6 +15125,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -14743,7 +15144,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1711097145</v>
+        <v>1713784387</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -14761,6 +15162,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14779,7 +15181,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1711145658</v>
+        <v>1713784403</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -14797,6 +15199,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14815,7 +15218,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1711146669</v>
+        <v>1713789063</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -14833,6 +15236,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14851,7 +15255,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1711147653</v>
+        <v>1713789077</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -14869,6 +15273,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14887,7 +15292,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1711171737</v>
+        <v>1713792247</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -14905,6 +15310,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14923,7 +15329,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1711171749</v>
+        <v>1713792257</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -14941,6 +15347,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14959,7 +15366,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1711172741</v>
+        <v>1713794523</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -14977,6 +15384,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14995,7 +15403,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>1711173689</v>
+        <v>1713794534</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -15013,6 +15421,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -15031,7 +15440,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1711175076</v>
+        <v>1713827768</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -15049,6 +15458,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -15067,7 +15477,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1711175087</v>
+        <v>1713828721</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -15085,6 +15495,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -15103,7 +15514,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1711175486</v>
+        <v>1713831665</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -15121,6 +15532,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -15139,7 +15551,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1711176709</v>
+        <v>1713832817</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -15157,6 +15569,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -15175,7 +15588,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1711177174</v>
+        <v>1713866060</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -15193,6 +15606,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -15211,7 +15625,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1711179205</v>
+        <v>1713866075</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -15229,6 +15643,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -15247,7 +15662,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>1711186737</v>
+        <v>1713869581</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -15265,6 +15680,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -15283,7 +15699,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1711186750</v>
+        <v>1713869593</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -15301,6 +15717,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -15319,7 +15736,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>1711188875</v>
+        <v>1713872161</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -15337,6 +15754,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -15355,7 +15773,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1711233401</v>
+        <v>1713872172</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -15373,6 +15791,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -15391,7 +15810,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1711235737</v>
+        <v>1713874897</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -15409,6 +15828,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -15427,7 +15847,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>1711236712</v>
+        <v>1713874908</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -15445,6 +15865,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -15463,7 +15884,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1711246747</v>
+        <v>1713876400</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -15481,6 +15902,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -15499,7 +15921,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1711246766</v>
+        <v>1713876425</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -15517,6 +15939,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -15535,7 +15958,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1711247043</v>
+        <v>1713876796</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -15553,6 +15976,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -15571,7 +15995,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1711247056</v>
+        <v>1713876806</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -15589,6 +16013,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -15607,7 +16032,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1711247443</v>
+        <v>1713914406</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -15625,6 +16050,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -15643,7 +16069,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>1711250617</v>
+        <v>1713915465</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -15661,6 +16087,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -15679,7 +16106,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1711250877</v>
+        <v>1713916454</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -15697,6 +16124,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -15715,7 +16143,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1711250894</v>
+        <v>1713917567</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -15733,6 +16161,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -15751,7 +16180,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1711262098</v>
+        <v>1713952471</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -15769,6 +16198,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15787,7 +16217,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1711262116</v>
+        <v>1713952498</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -15805,6 +16235,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15823,7 +16254,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1711262693</v>
+        <v>1713956224</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -15841,6 +16272,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15859,7 +16291,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1711264088</v>
+        <v>1713956241</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -15877,6 +16309,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15895,7 +16328,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1711270039</v>
+        <v>1713958938</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -15913,6 +16346,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15931,7 +16365,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1711270055</v>
+        <v>1713958946</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -15949,6 +16383,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15967,7 +16402,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1711271183</v>
+        <v>1713962228</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -15985,6 +16420,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -16003,7 +16439,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1711271199</v>
+        <v>1713962239</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -16021,6 +16457,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -16039,7 +16476,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1711272089</v>
+        <v>1713964251</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -16057,6 +16494,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -16075,7 +16513,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1711273989</v>
+        <v>1713964259</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -16093,6 +16531,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -16111,7 +16550,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1711274300</v>
+        <v>1713966409</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -16129,6 +16568,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -16147,7 +16587,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1711275656</v>
+        <v>1713966426</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -16165,6 +16605,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -16183,7 +16624,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1711276274</v>
+        <v>1714000683</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -16201,6 +16642,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -16219,7 +16661,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1711319821</v>
+        <v>1714001735</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -16237,6 +16679,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -16255,7 +16698,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1711322189</v>
+        <v>1714005271</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -16273,6 +16716,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -16291,7 +16735,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1711323019</v>
+        <v>1714006255</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -16309,6 +16753,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -16327,7 +16772,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1711333315</v>
+        <v>1714018262</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -16345,6 +16790,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -16363,7 +16809,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1711333326</v>
+        <v>1714018269</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -16381,6 +16827,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -16399,7 +16846,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>1711333567</v>
+        <v>1714022355</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -16417,6 +16864,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -16435,7 +16883,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1711336640</v>
+        <v>1714022377</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -16453,6 +16901,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16471,7 +16920,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>1711351030</v>
+        <v>1714032066</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -16489,6 +16938,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -16507,7 +16957,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1711351058</v>
+        <v>1714032091</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -16525,6 +16975,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -16543,7 +16994,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1711351704</v>
+        <v>1714035317</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -16561,6 +17012,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -16579,7 +17031,7 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1711353674</v>
+        <v>1714035334</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
@@ -16597,6 +17049,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -16615,7 +17068,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1711357474</v>
+        <v>1714042933</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -16633,6 +17086,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -16651,7 +17105,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>1711357503</v>
+        <v>1714042950</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -16669,6 +17123,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -16687,7 +17142,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1711358898</v>
+        <v>1714049494</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -16705,6 +17160,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -16723,7 +17179,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1711360000</v>
+        <v>1714049509</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -16741,6 +17197,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -16759,7 +17216,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1711362122</v>
+        <v>1714052695</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -16777,6 +17234,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -16795,7 +17253,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1711362135</v>
+        <v>1714052704</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -16813,6 +17271,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16831,7 +17290,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1711362879</v>
+        <v>1714054686</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -16849,6 +17308,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16867,7 +17327,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1711364662</v>
+        <v>1714054702</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -16885,6 +17345,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16903,7 +17364,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1711366999</v>
+        <v>1714086879</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -16921,6 +17382,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -16939,7 +17401,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1711410515</v>
+        <v>1714087922</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -16957,6 +17419,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16975,7 +17438,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1711411820</v>
+        <v>1714089416</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -16993,6 +17456,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -17011,7 +17475,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1711413011</v>
+        <v>1714090495</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -17029,6 +17493,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -17047,7 +17512,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1711451439</v>
+        <v>1714104308</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -17065,6 +17530,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -17083,7 +17549,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1711451446</v>
+        <v>1714104320</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -17101,6 +17567,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -17119,7 +17586,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1711451452</v>
+        <v>1714109421</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -17137,6 +17604,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -17155,7 +17623,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1711451466</v>
+        <v>1714109430</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -17173,6 +17641,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -17191,7 +17660,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1711452111</v>
+        <v>1714124671</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -17209,6 +17678,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -17227,7 +17697,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1711454287</v>
+        <v>1714124680</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -17245,6 +17715,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -17263,7 +17734,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1711454701</v>
+        <v>1714127351</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -17281,6 +17752,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -17299,7 +17771,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1711454716</v>
+        <v>1714127361</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -17317,6 +17789,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -17335,7 +17808,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1711456424</v>
+        <v>1714129282</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -17353,6 +17826,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -17371,7 +17845,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1711456434</v>
+        <v>1714129293</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -17389,6 +17863,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -17407,7 +17882,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1711457134</v>
+        <v>1714129814</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -17425,6 +17900,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -17443,7 +17919,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1711461377</v>
+        <v>1714129838</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -17461,6 +17937,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -17479,7 +17956,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1711463722</v>
+        <v>1714134308</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -17497,6 +17974,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -17515,7 +17993,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1711505951</v>
+        <v>1714134319</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -17533,6 +18011,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -17551,7 +18030,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1711510436</v>
+        <v>1714141369</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -17569,6 +18048,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -17587,7 +18067,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>1711511073</v>
+        <v>1714141396</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -17605,6 +18085,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -17623,7 +18104,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1711541352</v>
+        <v>1714177738</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -17641,6 +18122,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -17659,7 +18141,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1711541388</v>
+        <v>1714182941</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -17677,6 +18159,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -17695,7 +18178,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>1711542611</v>
+        <v>1714188032</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -17713,6 +18196,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -17731,7 +18215,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1711548060</v>
+        <v>1714188663</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -17749,6 +18233,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -17767,7 +18252,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1711548815</v>
+        <v>1714219517</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -17785,6 +18270,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -17803,7 +18289,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1711548826</v>
+        <v>1714219558</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -17821,6 +18307,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -17839,7 +18326,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>1711550434</v>
+        <v>1714225227</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -17857,6 +18344,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -17875,7 +18363,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>1711550488</v>
+        <v>1714225279</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -17893,6 +18381,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -17911,7 +18400,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>1711551805</v>
+        <v>1714226058</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -17929,6 +18418,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -17947,7 +18437,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>1711555485</v>
+        <v>1714226066</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -17965,6 +18455,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -17983,7 +18474,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>1711556108</v>
+        <v>1714226693</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -18001,6 +18492,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -18019,7 +18511,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1711563095</v>
+        <v>1714226706</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -18037,6 +18529,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -18055,7 +18548,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>1711585126</v>
+        <v>1714231030</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -18073,6 +18566,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -18091,7 +18585,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1711592461</v>
+        <v>1714231036</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -18109,6 +18603,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -18127,7 +18622,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1711596592</v>
+        <v>1714238852</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -18145,6 +18640,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -18163,7 +18659,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1711597218</v>
+        <v>1714238928</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -18181,6 +18677,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -18199,7 +18696,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1711627125</v>
+        <v>1714265204</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -18217,6 +18714,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -18235,7 +18733,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1711627211</v>
+        <v>1714270451</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -18253,6 +18751,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -18271,7 +18770,7 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1711628342</v>
+        <v>1714271831</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -18289,6 +18788,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -18307,7 +18807,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>1711634315</v>
+        <v>1714272556</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -18325,6 +18825,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -18343,7 +18844,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1711634987</v>
+        <v>1714304759</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -18361,6 +18862,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -18379,7 +18881,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1711635039</v>
+        <v>1714304826</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -18397,6 +18899,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -18415,7 +18918,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1711636404</v>
+        <v>1714306754</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -18433,6 +18936,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -18451,7 +18955,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1711640395</v>
+        <v>1714306794</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -18469,6 +18973,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -18487,7 +18992,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1711641111</v>
+        <v>1714312361</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -18505,6 +19010,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -18523,7 +19029,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>1711648215</v>
+        <v>1714312370</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -18541,6 +19047,229 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>1714313028</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>1714313035</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>1714313077</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>1714313092</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>1714322340</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>1714322407</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
